--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N101_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N101_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.43503307852217</v>
+        <v>8.033192875259852</v>
       </c>
       <c r="D2" t="n">
-        <v>49.42463368381814</v>
+        <v>8.031502973620448</v>
       </c>
       <c r="E2" t="n">
-        <v>13.31298352247243</v>
+        <v>2.163359822401771</v>
       </c>
       <c r="F2" t="n">
-        <v>12.46839124679256</v>
+        <v>2.026113577603792</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.18927410254246</v>
+        <v>7.83075704166315</v>
       </c>
       <c r="D3" t="n">
-        <v>47.93619154326461</v>
+        <v>7.789631125780499</v>
       </c>
       <c r="E3" t="n">
-        <v>13.31298352247243</v>
+        <v>2.163359822401771</v>
       </c>
       <c r="F3" t="n">
-        <v>12.46839124679256</v>
+        <v>2.026113577603792</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.30933067772369</v>
+        <v>2.3252662351301</v>
       </c>
       <c r="D4" t="n">
-        <v>20.57950204482721</v>
+        <v>3.344169082284421</v>
       </c>
       <c r="E4" t="n">
-        <v>13.31298352247243</v>
+        <v>2.163359822401771</v>
       </c>
       <c r="F4" t="n">
-        <v>12.46839124679256</v>
+        <v>2.026113577603792</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.84902163774913</v>
+        <v>6.150466016134234</v>
       </c>
       <c r="D5" t="n">
-        <v>21.07893507595601</v>
+        <v>3.425326949842852</v>
       </c>
       <c r="E5" t="n">
-        <v>13.31298352247243</v>
+        <v>2.163359822401771</v>
       </c>
       <c r="F5" t="n">
-        <v>12.46839124679256</v>
+        <v>2.026113577603792</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.14349791570383</v>
+        <v>7.823318411301873</v>
       </c>
       <c r="D6" t="n">
-        <v>35.4462312995475</v>
+        <v>5.760012586176469</v>
       </c>
       <c r="E6" t="n">
-        <v>13.31298352247243</v>
+        <v>2.163359822401771</v>
       </c>
       <c r="F6" t="n">
-        <v>12.46839124679256</v>
+        <v>2.026113577603792</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
